--- a/artfynd/A 9973-2026 artfynd.xlsx
+++ b/artfynd/A 9973-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>1205754</v>
       </c>
       <c r="B2" t="n">
-        <v>90648</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605730.6573062279</v>
+        <v>605731</v>
       </c>
       <c r="R2" t="n">
-        <v>6885206.448295438</v>
+        <v>6885206</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2009-08-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5049499</v>
+        <v>1890275</v>
       </c>
       <c r="B3" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606060.9400825619</v>
+        <v>605772</v>
       </c>
       <c r="R3" t="n">
-        <v>6885259.442886254</v>
+        <v>6885202</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,24 +858,9 @@
           <t>2009-08-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>större fläckar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +874,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>lövrik barrskog</t>
+          <t>äldre granskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # äldre asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,6 +897,231 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Biol. inventering inför vindkraftsutbyggnad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1942834</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mörkåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>606338</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6885265</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-08-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-08-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>asprik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>3 substratenheter # gamla aspar</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biol. inventering inför vindkraftsutbyggnad</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5049499</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörkåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>606061</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6885259</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bergsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-08-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-08-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>större fläckar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>lövrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Biol. inventering inför vindkraftsutbyggnad</t>
         </is>

--- a/artfynd/A 9973-2026 artfynd.xlsx
+++ b/artfynd/A 9973-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Biol. inventering inför vindkraftsutbyggnad</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1205754</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
           <t>Biol. inventering inför vindkraftsutbyggnad</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1890275</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Biol. inventering inför vindkraftsutbyggnad</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1942834</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
           <t>Biol. inventering inför vindkraftsutbyggnad</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5049499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>